--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>单据编号</t>
   </si>
@@ -60,12 +60,15 @@
     <t>创建人</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>处理人</t>
+  </si>
+  <si>
     <t>处理时间</t>
   </si>
   <si>
-    <t>创建时间</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -108,10 +111,10 @@
     <t>{.handleUserName}</t>
   </si>
   <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
     <t>{.handleTime}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1147,7 +1150,8 @@
     <col min="13" max="13" width="28" customWidth="1"/>
     <col min="14" max="14" width="10.5" customWidth="1"/>
     <col min="15" max="15" width="21.25" customWidth="1"/>
-    <col min="16" max="16" width="23.75" customWidth="1"/>
+    <col min="16" max="16" width="10.625" customWidth="1"/>
+    <col min="17" max="17" width="22.25" customWidth="1"/>
     <col min="18" max="18" width="8.875" customWidth="1"/>
     <col min="19" max="19" width="31.25" customWidth="1"/>
     <col min="21" max="21" width="17.25" customWidth="1"/>
@@ -1155,7 +1159,7 @@
     <col min="24" max="24" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1204,55 +1208,61 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:16">
+    <row r="2" s="2" customFormat="1" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>31</v>
+      <c r="Q2" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>单据编号</t>
   </si>
@@ -33,6 +46,18 @@
     <t>来源单号</t>
   </si>
   <si>
+    <t>第三方仓SKU</t>
+  </si>
+  <si>
+    <t>平台产品ID</t>
+  </si>
+  <si>
+    <t>平台SKU</t>
+  </si>
+  <si>
+    <t>FNSKU</t>
+  </si>
+  <si>
     <t>sku</t>
   </si>
   <si>
@@ -82,6 +107,18 @@
   </si>
   <si>
     <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.thirdWarehouseSku}</t>
+  </si>
+  <si>
+    <t>{.platformProductId}</t>
+  </si>
+  <si>
+    <t>{.platformSku}</t>
+  </si>
+  <si>
+    <t>{.platformFnSku}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -120,14 +157,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +184,22 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF4A4A4A"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -638,137 +691,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -781,7 +834,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1132,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1140,26 +1199,27 @@
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="8.125" customWidth="1"/>
     <col min="5" max="5" width="20.75" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="13.125" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="26.75" customWidth="1"/>
-    <col min="12" max="12" width="27.375" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="15" width="21.25" customWidth="1"/>
-    <col min="16" max="16" width="10.625" customWidth="1"/>
-    <col min="17" max="17" width="22.25" customWidth="1"/>
-    <col min="18" max="18" width="8.875" customWidth="1"/>
-    <col min="19" max="19" width="31.25" customWidth="1"/>
-    <col min="21" max="21" width="17.25" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
+    <col min="6" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="14.375" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="26.75" customWidth="1"/>
+    <col min="16" max="16" width="27.375" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
+    <col min="19" max="19" width="21.25" customWidth="1"/>
+    <col min="20" max="20" width="10.625" customWidth="1"/>
+    <col min="21" max="21" width="22.25" customWidth="1"/>
+    <col min="22" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="31.25" customWidth="1"/>
+    <col min="25" max="25" width="17.25" customWidth="1"/>
+    <col min="27" max="27" width="9.375" customWidth="1"/>
+    <col min="28" max="28" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1175,16 +1235,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -1211,58 +1271,82 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
-      <c r="A2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="4" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:21">
+      <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="K2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
+      <c r="L2" s="6" t="s">
         <v>32</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>单据编号</t>
   </si>
@@ -46,6 +46,9 @@
     <t>来源单号</t>
   </si>
   <si>
+    <t>货件单号</t>
+  </si>
+  <si>
     <t>第三方仓SKU</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
   </si>
   <si>
     <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.fbaShipmentCode}</t>
   </si>
   <si>
     <t>{.thirdWarehouseSku}</t>
@@ -1191,35 +1197,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="8.5" customWidth="1"/>
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="8.125" customWidth="1"/>
-    <col min="5" max="5" width="20.75" customWidth="1"/>
-    <col min="6" max="9" width="13.875" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
-    <col min="12" max="12" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="10.25" customWidth="1"/>
-    <col min="15" max="15" width="26.75" customWidth="1"/>
-    <col min="16" max="16" width="27.375" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="21.25" customWidth="1"/>
-    <col min="20" max="20" width="10.625" customWidth="1"/>
-    <col min="21" max="21" width="22.25" customWidth="1"/>
-    <col min="22" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="31.25" customWidth="1"/>
-    <col min="25" max="25" width="17.25" customWidth="1"/>
-    <col min="27" max="27" width="9.375" customWidth="1"/>
-    <col min="28" max="28" width="14.375" customWidth="1"/>
+    <col min="5" max="6" width="20.75" customWidth="1"/>
+    <col min="7" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="42" customWidth="1"/>
+    <col min="13" max="13" width="14.375" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="26.75" customWidth="1"/>
+    <col min="17" max="17" width="27.375" customWidth="1"/>
+    <col min="18" max="18" width="28" customWidth="1"/>
+    <col min="19" max="19" width="10.5" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="21" width="10.625" customWidth="1"/>
+    <col min="22" max="22" width="22.25" customWidth="1"/>
+    <col min="23" max="23" width="8.875" customWidth="1"/>
+    <col min="24" max="24" width="31.25" customWidth="1"/>
+    <col min="26" max="26" width="17.25" customWidth="1"/>
+    <col min="28" max="28" width="9.375" customWidth="1"/>
+    <col min="29" max="29" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1235,19 +1241,19 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1283,70 +1289,76 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:21">
+    <row r="2" s="2" customFormat="1" spans="1:22">
       <c r="A2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U2" s="6" t="s">
         <v>40</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>单据编号</t>
   </si>
@@ -49,15 +49,12 @@
     <t>货件单号</t>
   </si>
   <si>
-    <t>第三方仓SKU</t>
+    <t>平台(第三方仓)SKU</t>
   </si>
   <si>
     <t>平台产品ID</t>
   </si>
   <si>
-    <t>平台SKU</t>
-  </si>
-  <si>
     <t>FNSKU</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>{.platformProductId}</t>
-  </si>
-  <si>
-    <t>{.platformSku}</t>
   </si>
   <si>
     <t>{.platformFnSku}</t>
@@ -1197,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1205,27 +1199,27 @@
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="8.125" customWidth="1"/>
     <col min="5" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="10" width="13.875" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="12" width="42" customWidth="1"/>
-    <col min="13" max="13" width="14.375" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="26.75" customWidth="1"/>
-    <col min="17" max="17" width="27.375" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="19" width="10.5" customWidth="1"/>
-    <col min="20" max="20" width="21.25" customWidth="1"/>
-    <col min="21" max="21" width="10.625" customWidth="1"/>
-    <col min="22" max="22" width="22.25" customWidth="1"/>
-    <col min="23" max="23" width="8.875" customWidth="1"/>
-    <col min="24" max="24" width="31.25" customWidth="1"/>
-    <col min="26" max="26" width="17.25" customWidth="1"/>
-    <col min="28" max="28" width="9.375" customWidth="1"/>
-    <col min="29" max="29" width="14.375" customWidth="1"/>
+    <col min="7" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="14.375" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="26.75" customWidth="1"/>
+    <col min="16" max="16" width="27.375" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
+    <col min="19" max="19" width="21.25" customWidth="1"/>
+    <col min="20" max="20" width="10.625" customWidth="1"/>
+    <col min="21" max="21" width="22.25" customWidth="1"/>
+    <col min="22" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="31.25" customWidth="1"/>
+    <col min="25" max="25" width="17.25" customWidth="1"/>
+    <col min="27" max="27" width="9.375" customWidth="1"/>
+    <col min="28" max="28" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1250,10 +1244,10 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1289,76 +1283,70 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:21">
+      <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:22">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="T2" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27045" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,15 +49,12 @@
     <t>货件单号</t>
   </si>
   <si>
-    <t>第三方仓SKU</t>
+    <t>平台(第三方仓)SKU</t>
   </si>
   <si>
     <t>平台产品ID</t>
   </si>
   <si>
-    <t>平台SKU</t>
-  </si>
-  <si>
     <t>FNSKU</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
     <t>调出仓库</t>
   </si>
   <si>
+    <t>调出虚拟仓</t>
+  </si>
+  <si>
     <t>调入仓库</t>
   </si>
   <si>
@@ -121,9 +121,6 @@
     <t>{.platformProductId}</t>
   </si>
   <si>
-    <t>{.platformSku}</t>
-  </si>
-  <si>
     <t>{.platformFnSku}</t>
   </si>
   <si>
@@ -146,6 +143,9 @@
   </si>
   <si>
     <t>{.fromWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.fromVirtualWarehouseName}</t>
   </si>
   <si>
     <t>{.toWarehouseName}</t>
@@ -1205,14 +1205,15 @@
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="8.125" customWidth="1"/>
     <col min="5" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="10" width="13.875" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="12" width="42" customWidth="1"/>
-    <col min="13" max="13" width="14.375" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="26.75" customWidth="1"/>
-    <col min="17" max="17" width="27.375" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="14.375" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="26.75" customWidth="1"/>
+    <col min="16" max="17" width="27.375" customWidth="1"/>
     <col min="18" max="18" width="28" customWidth="1"/>
     <col min="19" max="19" width="10.5" customWidth="1"/>
     <col min="20" max="20" width="21.25" customWidth="1"/>
@@ -1250,10 +1251,10 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">

--- a/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/requisitionApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27525" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>单据编号</t>
   </si>
@@ -79,6 +79,9 @@
     <t>调出仓库</t>
   </si>
   <si>
+    <t>调出虚拟仓</t>
+  </si>
+  <si>
     <t>调入仓库</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
   </si>
   <si>
     <t>{.fromWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.fromVirtualWarehouseName}</t>
   </si>
   <si>
     <t>{.toWarehouseName}</t>
@@ -1191,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1206,20 +1212,20 @@
     <col min="13" max="13" width="13.125" customWidth="1"/>
     <col min="14" max="14" width="10.25" customWidth="1"/>
     <col min="15" max="15" width="26.75" customWidth="1"/>
-    <col min="16" max="16" width="27.375" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="21.25" customWidth="1"/>
-    <col min="20" max="20" width="10.625" customWidth="1"/>
-    <col min="21" max="21" width="22.25" customWidth="1"/>
-    <col min="22" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="31.25" customWidth="1"/>
-    <col min="25" max="25" width="17.25" customWidth="1"/>
-    <col min="27" max="27" width="9.375" customWidth="1"/>
-    <col min="28" max="28" width="14.375" customWidth="1"/>
+    <col min="16" max="17" width="27.375" customWidth="1"/>
+    <col min="18" max="18" width="28" customWidth="1"/>
+    <col min="19" max="19" width="10.5" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="21" width="10.625" customWidth="1"/>
+    <col min="22" max="22" width="22.25" customWidth="1"/>
+    <col min="23" max="23" width="8.875" customWidth="1"/>
+    <col min="24" max="24" width="31.25" customWidth="1"/>
+    <col min="26" max="26" width="17.25" customWidth="1"/>
+    <col min="28" max="28" width="9.375" customWidth="1"/>
+    <col min="29" max="29" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1283,70 +1289,76 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:21">
+    <row r="2" s="2" customFormat="1" spans="1:22">
       <c r="A2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U2" s="6" t="s">
         <v>40</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
